--- a/artfynd/A 29873-2022 artfynd.xlsx
+++ b/artfynd/A 29873-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29873-2022 artfynd.xlsx
+++ b/artfynd/A 29873-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60654512</v>
+        <v>61577264</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>ruokovaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>808720.0159670542</v>
+        <v>808720</v>
       </c>
       <c r="R2" t="n">
-        <v>7484279.711605817</v>
+        <v>7484280</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,28 +746,17 @@
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,15 +775,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60654538</v>
+        <v>62188627</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,39 +786,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ruokovaara, Nb</t>
+          <t>Saittarova, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>808720.0159670542</v>
+        <v>808720</v>
       </c>
       <c r="R3" t="n">
-        <v>7484279.711605817</v>
+        <v>7484290</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,19 +854,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare</t>
+          <t>Camilla Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,12 +875,7 @@
         <v>60654518</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,12 +892,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>808720.0159670542</v>
+        <v>808720</v>
       </c>
       <c r="R4" t="n">
-        <v>7484279.711605817</v>
+        <v>7484280</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +942,9 @@
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61577264</v>
+        <v>60654512</v>
       </c>
       <c r="B5" t="n">
-        <v>98427</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,37 +983,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>ruokovaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>808720.0159670542</v>
+        <v>808720</v>
       </c>
       <c r="R5" t="n">
-        <v>7484279.711605817</v>
+        <v>7484280</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,27 +1042,18 @@
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,12 +1075,7 @@
         <v>60654555</v>
       </c>
       <c r="B6" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808720.0159670542</v>
+        <v>808720</v>
       </c>
       <c r="R6" t="n">
-        <v>7484279.711605817</v>
+        <v>7484280</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,19 +1143,9 @@
           <t>2016-07-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-07-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,118 +1169,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>62188627</v>
-      </c>
-      <c r="B7" t="n">
-        <v>98427</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Röd trolldruva</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Actaea erythrocarpa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fisch.) Kom.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Saittarova, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>808720.0076737382</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7484289.832435379</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Tärendö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2016-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Camilla Carlsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29873-2022 artfynd.xlsx
+++ b/artfynd/A 29873-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61577264</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62188627</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60654518</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60654512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,8 +1194,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60654555</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>